--- a/docs/Phase0_03_フロー設計書.xlsx
+++ b/docs/Phase0_03_フロー設計書.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/562294414948a666/ドキュメント/myWeb/RecipeSite/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="40" documentId="11_AD4D066CA252ABDACC104868B151CE7672EEDF52" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7BAC2919-99B1-4EA0-8773-0B5AA4812290}"/>
+  <xr:revisionPtr revIDLastSave="141" documentId="11_AD4D066CA252ABDACC104868B151CE7672EEDF52" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C21B0029-7ED2-416D-A8BD-42FFFB6E2EA0}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="フローリスト" sheetId="1" r:id="rId1"/>
+    <sheet name="split2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="46">
   <si>
     <t>フローリスト</t>
     <phoneticPr fontId="1"/>
@@ -186,6 +187,200 @@
     <rPh sb="20" eb="22">
       <t>タイキ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>05</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>担当split</t>
+    <rPh sb="0" eb="2">
+      <t>タントウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>01</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>02</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>レシピサムネイル一覧表示フロー</t>
+  </si>
+  <si>
+    <t>レシピサムネイル一覧部分にレシピサムネイルを表示させるフロー</t>
+  </si>
+  <si>
+    <t>split1</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>split1では簡易データのみの設計</t>
+    <rPh sb="8" eb="10">
+      <t>カンイ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>セッケイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>03</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>04</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>詳細ページ閲覧フロー</t>
+    <rPh sb="0" eb="2">
+      <t>ショウサイ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>エツラン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>TOPページ→詳細ページ遷移フロー</t>
+    <rPh sb="7" eb="9">
+      <t>ショウサイ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>詳細ページ→TOPページ遷移フロー</t>
+    <rPh sb="0" eb="2">
+      <t>ショウサイ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>詳細ページ→献立表ページ遷移フロー</t>
+    <rPh sb="0" eb="2">
+      <t>ショウサイ</t>
+    </rPh>
+    <rPh sb="6" eb="9">
+      <t>コンダテヒョウ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>06</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>献立表ページ→詳細ページ遷移フロー</t>
+    <rPh sb="0" eb="2">
+      <t>コンダテ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ヒョウ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ショウサイ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>TOPページから詳細ページに遷移させるフロー</t>
+    <rPh sb="8" eb="10">
+      <t>ショウサイ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>詳細ページからTOPページに遷移させるフロー</t>
+    <rPh sb="0" eb="2">
+      <t>ショウサイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>split2</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>split3</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>split2の時点では献立表ページは空白にするのでsplit3で実装</t>
+    <rPh sb="7" eb="9">
+      <t>ジテン</t>
+    </rPh>
+    <rPh sb="11" eb="14">
+      <t>コンダテヒョウ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>クウハク</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>ジッソウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>閲覧したいレシピの詳細ページを表示させるためのフロー</t>
+    <rPh sb="0" eb="2">
+      <t>エツラン</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ショウサイ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>詳細ページから献立表ページに遷移させるフロー</t>
+    <rPh sb="7" eb="10">
+      <t>コンダテヒョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>献立表ページから詳細ページに遷移させるフロー</t>
+    <rPh sb="0" eb="3">
+      <t>コンダテヒョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>02_TOPページ→詳細ページ遷移フロー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>03_詳細ページ→TOPページ遷移フロー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>04_詳細ページ閲覧フロー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>05_詳細ページ→献立表ページ遷移フロー</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -261,7 +456,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -269,6 +464,9 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -284,6 +482,187 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>562104</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>82787</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="図 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7CD93925-C0FE-B797-D445-A357DC99F654}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="676275" y="504825"/>
+          <a:ext cx="2511554" cy="4610337"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>25400</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>92075</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>539878</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>73212</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="図 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{46363C05-0D3B-526A-4798-484652EE6555}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3968750" y="549275"/>
+          <a:ext cx="2489328" cy="3638737"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>216046</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>190729</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="図 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4D59682A-4203-4874-D9A7-80E9C569526E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7239000" y="523875"/>
+          <a:ext cx="2838596" cy="4467454"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>47625</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>428746</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>124005</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="図 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BC2BABA1-D93A-24EE-6AD4-62E6445AD022}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10134600" y="495300"/>
+          <a:ext cx="2352796" cy="3514905"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -549,21 +928,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:E8"/>
+  <dimension ref="B2:F18"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="2" max="2" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="29.75" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="33.83203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="81.08203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="37.25" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="56.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:5">
+    <row r="2" spans="2:6">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="2:5">
+    <row r="4" spans="2:6">
       <c r="B4" s="2" t="s">
         <v>1</v>
       </c>
@@ -574,62 +954,196 @@
         <v>3</v>
       </c>
       <c r="E4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="2:5">
-      <c r="B5" s="3" t="s">
+    <row r="5" spans="2:6">
+      <c r="B5" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="2:6">
+      <c r="B6" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F6" s="2"/>
+    </row>
+    <row r="7" spans="2:6">
+      <c r="B7" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F7" s="2"/>
+    </row>
+    <row r="8" spans="2:6">
+      <c r="B8" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F8" s="2"/>
+    </row>
+    <row r="9" spans="2:6">
+      <c r="B9" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F9" s="2"/>
+    </row>
+    <row r="10" spans="2:6">
+      <c r="B10" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="14" spans="2:6">
+      <c r="B14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C14" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D14" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="E5" s="2"/>
-    </row>
-    <row r="6" spans="2:5">
-      <c r="B6" s="3" t="s">
+      <c r="F14" s="2"/>
+    </row>
+    <row r="15" spans="2:6">
+      <c r="B15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C15" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D15" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E6" s="2"/>
-    </row>
-    <row r="7" spans="2:5">
-      <c r="B7" s="3" t="s">
+      <c r="F15" s="2"/>
+    </row>
+    <row r="16" spans="2:6">
+      <c r="B16" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C16" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D16" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="F16" s="4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="2:5">
-      <c r="B8" s="3" t="s">
+    <row r="17" spans="2:6">
+      <c r="B17" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C17" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D17" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="E8" s="2"/>
+      <c r="F17" s="2"/>
+    </row>
+    <row r="18" spans="2:6">
+      <c r="B18" s="3"/>
+      <c r="C18" s="5"/>
+      <c r="D18" s="5"/>
+      <c r="F18" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DE679CD-6208-4268-A6FF-F280E7D5D796}">
+  <dimension ref="B2:R2"/>
+  <sheetFormatPr defaultRowHeight="18"/>
+  <cols>
+    <col min="6" max="6" width="4" customWidth="1"/>
+    <col min="11" max="11" width="3.5" customWidth="1"/>
+    <col min="17" max="17" width="4.1640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:18">
+      <c r="B2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L2" t="s">
+        <v>44</v>
+      </c>
+      <c r="R2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/docs/Phase0_03_フロー設計書.xlsx
+++ b/docs/Phase0_03_フロー設計書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/562294414948a666/ドキュメント/myWeb/RecipeSite/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="141" documentId="11_AD4D066CA252ABDACC104868B151CE7672EEDF52" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C21B0029-7ED2-416D-A8BD-42FFFB6E2EA0}"/>
+  <xr:revisionPtr revIDLastSave="143" documentId="11_AD4D066CA252ABDACC104868B151CE7672EEDF52" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B05132F1-D863-4053-B14A-423E26607148}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="フローリスト" sheetId="1" r:id="rId1"/>
@@ -456,7 +456,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -464,9 +464,7 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -576,50 +574,6 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>9525</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>66675</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>216046</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>190729</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="図 5">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4D59682A-4203-4874-D9A7-80E9C569526E}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="7239000" y="523875"/>
-          <a:ext cx="2838596" cy="4467454"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
       <xdr:col>17</xdr:col>
       <xdr:colOff>47625</xdr:colOff>
       <xdr:row>2</xdr:row>
@@ -645,7 +599,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -654,6 +608,50 @@
         <a:xfrm>
           <a:off x="10134600" y="495300"/>
           <a:ext cx="2352796" cy="3514905"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>15875</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>130316</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>101827</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="図 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4C8A9BAB-746D-E537-C1B1-9BC748D4CAD7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6502400" y="476250"/>
+          <a:ext cx="2743341" cy="4426177"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -961,7 +959,7 @@
       </c>
     </row>
     <row r="5" spans="2:6">
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="5" t="s">
         <v>20</v>
       </c>
       <c r="C5" s="2" t="s">
@@ -978,7 +976,7 @@
       </c>
     </row>
     <row r="6" spans="2:6">
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="5" t="s">
         <v>21</v>
       </c>
       <c r="C6" s="2" t="s">
@@ -993,7 +991,7 @@
       <c r="F6" s="2"/>
     </row>
     <row r="7" spans="2:6">
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="5" t="s">
         <v>26</v>
       </c>
       <c r="C7" s="2" t="s">
@@ -1008,7 +1006,7 @@
       <c r="F7" s="2"/>
     </row>
     <row r="8" spans="2:6">
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="5" t="s">
         <v>27</v>
       </c>
       <c r="C8" s="2" t="s">
@@ -1023,7 +1021,7 @@
       <c r="F8" s="2"/>
     </row>
     <row r="9" spans="2:6">
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="5" t="s">
         <v>18</v>
       </c>
       <c r="C9" s="2" t="s">
@@ -1038,7 +1036,7 @@
       <c r="F9" s="2"/>
     </row>
     <row r="10" spans="2:6">
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="5" t="s">
         <v>32</v>
       </c>
       <c r="C10" s="2" t="s">
@@ -1106,8 +1104,8 @@
     </row>
     <row r="18" spans="2:6">
       <c r="B18" s="3"/>
-      <c r="C18" s="5"/>
-      <c r="D18" s="5"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
       <c r="F18" s="2"/>
     </row>
   </sheetData>
